--- a/data/trans_orig/IP22D2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP22D2_2023-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12814</t>
+          <t>12647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>21864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7435</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>743</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>521</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>744</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>71,74%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>402</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>769</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>66,21%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>300</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,23%</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10429</t>
+          <t>10574</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>20285</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>520</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>368</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>896</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>29465</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>33880</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>56130</t>
+          <t>54485</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>44136</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>64581</t>
+          <t>65998</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP22D2_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8172</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9572</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4819</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12647</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>70,78%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>11894</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21864</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3297</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>24,38%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>57,45%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3425</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,33%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>618</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,47 +1289,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>22,84%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>732</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4743</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>30,74%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>62,39%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -1402,67 +1402,67 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7648</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6131</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7946</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>96,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>77,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5265</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2859</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6870</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>69,26%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>90,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,74 +1858,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1844</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>63,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18,49%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>57,68%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1860</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>56,16%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>12,29%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2334</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,14%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3128</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7281</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>38,92%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>9,47%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1792</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4130</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>30,33%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>69,89%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>351</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4460</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7117</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>55,48%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>88,53%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>4117</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1781</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5507</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>69,67%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>30,14%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>93,2%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -2766,82 +2766,82 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3628</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>42,66%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,34 +3001,34 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>527</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>31,39%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3109,82 +3109,82 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1631</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>68,88%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>520</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>520</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,47 +3565,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1783</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>61,06%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2238</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>21,78%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>69,56%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>516</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>764</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>215</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -3683,27 +3683,27 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3718,27 +3718,27 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -4017,57 +4017,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2920</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>2920</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2920</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4134,72 +4134,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>4599</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1582</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>12,43%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>65,28%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2514</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>5442</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>22,5%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>48,7%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -4247,72 +4247,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>7188</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>10332</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>56,46%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>28,42%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>81,16%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>8661</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>5733</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>10574</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>77,5%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>51,3%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>16843</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>11155</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -4360,82 +4360,82 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>4847</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>35,62%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>944</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>882</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>524</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>68,31%</t>
         </is>
       </c>
     </row>
@@ -4821,27 +4821,27 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4856,27 +4856,27 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>440</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5272,72 +5272,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>19700</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>14017</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>26402</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>29,25%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>55,09%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>20332</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>13515</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>30398</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>42,21%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>63,11%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>22327</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>34060</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>54485</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -5385,72 +5385,72 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>26827</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>19354</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>32518</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>55,98%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>40,39%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>67,86%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>27179</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>16782</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>33783</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>56,43%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>34,84%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>70,14%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>56121</t>
+          <t>54879</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>44136</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>65998</t>
+          <t>63492</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -5498,82 +5498,82 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>944</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -5583,12 +5583,12 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>618</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
